--- a/USUARIOS.xlsx
+++ b/USUARIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ing Fredy Flores\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BD0EEE1-945F-4FBE-A938-4FEDE97A4B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126D78EB-23FF-4193-9D45-355928404777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3BB293FE-CDC7-4FED-A846-1644B3DDFEE3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>USUARIO</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t xml:space="preserve">XIMENA CORONA </t>
+  </si>
+  <si>
+    <t>CLAVE</t>
   </si>
 </sst>
 </file>
@@ -388,35 +391,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A814EE2-D08D-4592-93EE-9C9E248A068B}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
         <v>5567439014</v>
       </c>
+      <c r="C2">
+        <v>2579</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>5555555555</v>
+      </c>
+      <c r="C3">
+        <v>4967</v>
       </c>
     </row>
   </sheetData>

--- a/USUARIOS.xlsx
+++ b/USUARIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ing Fredy Flores\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126D78EB-23FF-4193-9D45-355928404777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908D46CC-E26E-4056-A6DF-0E4A85D3D7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3BB293FE-CDC7-4FED-A846-1644B3DDFEE3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>USUARIO</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>CLAVE</t>
+  </si>
+  <si>
+    <t>EDUARDO CORONA ACEVEDO</t>
   </si>
 </sst>
 </file>
@@ -391,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A814EE2-D08D-4592-93EE-9C9E248A068B}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" customWidth="1"/>
@@ -431,6 +434,17 @@
         <v>4967</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>5555555555</v>
+      </c>
+      <c r="C4">
+        <v>5873</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/USUARIOS.xlsx
+++ b/USUARIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ing Fredy Flores\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908D46CC-E26E-4056-A6DF-0E4A85D3D7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83555017-5566-4CE0-947E-010F20CE3CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3BB293FE-CDC7-4FED-A846-1644B3DDFEE3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>USUARIO</t>
   </si>
@@ -43,6 +43,12 @@
   </si>
   <si>
     <t>EDUARDO CORONA ACEVEDO</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES BASURTO</t>
+  </si>
+  <si>
+    <t>INES PACHECO</t>
   </si>
 </sst>
 </file>
@@ -394,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A814EE2-D08D-4592-93EE-9C9E248A068B}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" customWidth="1"/>
@@ -445,6 +451,28 @@
         <v>5873</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>5555555555</v>
+      </c>
+      <c r="C5">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>5555555555</v>
+      </c>
+      <c r="C6">
+        <v>1528</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/USUARIOS.xlsx
+++ b/USUARIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ing Fredy Flores\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83555017-5566-4CE0-947E-010F20CE3CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6CB07D-82AF-44E4-8ECA-6013AFF90E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3BB293FE-CDC7-4FED-A846-1644B3DDFEE3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>USUARIO</t>
   </si>
@@ -49,6 +49,12 @@
   </si>
   <si>
     <t>INES PACHECO</t>
+  </si>
+  <si>
+    <t>ISIDRO DIAZ CRUZ</t>
+  </si>
+  <si>
+    <t>ALISON YARET MORALES VALENCIA</t>
   </si>
 </sst>
 </file>
@@ -400,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A814EE2-D08D-4592-93EE-9C9E248A068B}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" customWidth="1"/>
@@ -473,6 +479,28 @@
         <v>1528</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>5646653398</v>
+      </c>
+      <c r="C7">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>5576032821</v>
+      </c>
+      <c r="C8">
+        <v>1625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
